--- a/Project Status_May_Sept_2026.xlsx
+++ b/Project Status_May_Sept_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms2dr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEAD39A-6F15-4F31-A20A-3DD05B03779E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EE3B45-B6B5-4500-99D0-6EAC9CB51E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4342F20-06FA-423A-A157-B4E154D3B885}"/>
   </bookViews>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>0</v>
@@ -804,13 +804,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>2</v>
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>2</v>
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>0</v>
@@ -1300,16 +1300,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>2</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>2</v>
@@ -1504,7 +1504,7 @@
         <v>4</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>2</v>

--- a/Project Status_May_Sept_2026.xlsx
+++ b/Project Status_May_Sept_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms2dr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EE3B45-B6B5-4500-99D0-6EAC9CB51E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4ABC4C-F244-48BD-A2A8-8B11ACFA976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4342F20-06FA-423A-A157-B4E154D3B885}"/>
   </bookViews>
@@ -1067,10 +1067,10 @@
         <v>2</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>2</v>
@@ -1135,7 +1135,7 @@
         <v>6</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>2</v>

--- a/Project Status_May_Sept_2026.xlsx
+++ b/Project Status_May_Sept_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms2dr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4ABC4C-F244-48BD-A2A8-8B11ACFA976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE31E316-7797-4037-A0D5-A8D91192D756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4342F20-06FA-423A-A157-B4E154D3B885}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="47">
   <si>
     <t>ü</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>Needs to Assign</t>
+  </si>
+  <si>
+    <t>[3A-CC1-26040] Classified Cycling-7SP HUB ASSEMBLY &amp; EO</t>
   </si>
 </sst>
 </file>
@@ -618,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4225F8-C54F-45A4-AF71-34F73F3782F7}">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -1534,6 +1537,68 @@
         <v>2</v>
       </c>
     </row>
+    <row r="16" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="C1:C15" xr:uid="{1A4225F8-C54F-45A4-AF71-34F73F3782F7}"/>
   <mergeCells count="3">
